--- a/reports/04_Predictive_Modelling_Results.xlsx
+++ b/reports/04_Predictive_Modelling_Results.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,31 +458,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mean Absolute Error (MAE)</t>
+          <t>Adjusted R²</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.196</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mean Squared Error (MSE)</t>
+          <t>Mean Absolute Error (MAE)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.925</v>
+        <v>2.196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Mean Squared Error (MSE)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7.925</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Root Mean Squared Error (RMSE)</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>2.815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mean Absolute Percentage Error (MAPE)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Weighted Absolute Percentage Error (WAPE)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.36</v>
       </c>
     </row>
   </sheetData>

--- a/reports/04_Predictive_Modelling_Results.xlsx
+++ b/reports/04_Predictive_Modelling_Results.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.871</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.823</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="4">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.196</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.925</v>
+        <v>7.407</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.815</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.5</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.36</v>
+        <v>11.01</v>
       </c>
     </row>
   </sheetData>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.545</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="4">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.262</v>
+        <v>12.605</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.356</v>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mean Absolute Percentage Error (MAPE)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Weighted Absolute Percentage Error (WAPE)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13.7</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +646,31 @@
           <t>MSE</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MAPE (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WAPE (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Training Time (s)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Prediction Time (s)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Peak Memory (MB)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -634,19 +679,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.871</v>
+        <v>0.879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.823</v>
+        <v>0.829</v>
       </c>
       <c r="D2" t="n">
-        <v>2.196</v>
+        <v>2.13</v>
       </c>
       <c r="E2" t="n">
-        <v>2.815</v>
+        <v>2.722</v>
       </c>
       <c r="F2" t="n">
-        <v>7.925</v>
+        <v>7.407</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.210584</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.001217</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0387</v>
       </c>
     </row>
     <row r="3">
@@ -656,17 +716,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2.545</v>
+        <v>2.65</v>
       </c>
       <c r="E3" t="n">
-        <v>3.356</v>
+        <v>3.55</v>
       </c>
       <c r="F3" t="n">
-        <v>11.262</v>
+        <v>12.605</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.708553</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.19045</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.276</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,10 +790,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.81586014827442</v>
+        <v>17.8359755371282</v>
       </c>
       <c r="D2" t="n">
-        <v>17.81586014827442</v>
+        <v>17.8359755371282</v>
       </c>
     </row>
     <row r="3">
@@ -731,10 +806,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-17.61271238343596</v>
+        <v>-17.26306136469564</v>
       </c>
       <c r="D3" t="n">
-        <v>17.61271238343596</v>
+        <v>17.26306136469564</v>
       </c>
     </row>
     <row r="4">
@@ -747,10 +822,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.743457432508238</v>
+        <v>4.431115318197251</v>
       </c>
       <c r="D4" t="n">
-        <v>4.743457432508238</v>
+        <v>4.431115318197251</v>
       </c>
     </row>
     <row r="5">
@@ -759,14 +834,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Renters_Pct</t>
+          <t>Visible_Minority_Pct</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.130430283786954</v>
+        <v>3.689616056275449</v>
       </c>
       <c r="D5" t="n">
-        <v>3.130430283786954</v>
+        <v>3.689616056275449</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +854,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.120192683244661</v>
+        <v>2.908447849106945</v>
       </c>
       <c r="D6" t="n">
-        <v>3.120192683244661</v>
+        <v>2.908447849106945</v>
       </c>
     </row>
     <row r="7">
@@ -791,14 +866,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visible_Minority_Pct</t>
+          <t>Immigrant_Population_Pct</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.955175392978107</v>
+        <v>-2.538853289649628</v>
       </c>
       <c r="D7" t="n">
-        <v>2.955175392978107</v>
+        <v>2.538853289649628</v>
       </c>
     </row>
     <row r="8">
@@ -807,14 +882,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Immigrant_Population_Pct</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.141444940507952</v>
+        <v>-2.490137557010714</v>
       </c>
       <c r="D8" t="n">
-        <v>2.141444940507952</v>
+        <v>2.490137557010714</v>
       </c>
     </row>
     <row r="9">
@@ -823,14 +898,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lone_Parent_Families_Pct</t>
+          <t>Core_Housing_Need</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.266299574130453</v>
+        <v>2.215033952599091</v>
       </c>
       <c r="D9" t="n">
-        <v>1.266299574130453</v>
+        <v>2.215033952599091</v>
       </c>
     </row>
     <row r="10">
@@ -839,14 +914,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>No_Diploma_Pct</t>
+          <t>Renters_Pct</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.3705297771218086</v>
+        <v>2.13260689947958</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3705297771218086</v>
+        <v>2.13260689947958</v>
       </c>
     </row>
     <row r="11">
@@ -855,14 +930,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bachelors_Degree_Pct</t>
+          <t>Lone_Parent_Families_Pct</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.2860370610864267</v>
+        <v>1.138175032138535</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2860370610864267</v>
+        <v>1.138175032138535</v>
       </c>
     </row>
     <row r="12">
@@ -871,14 +946,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Core_Housing_Need</t>
+          <t>Bachelors_Degree_Pct</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.2581753674404612</v>
+        <v>0.6143065159184056</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2581753674404612</v>
+        <v>0.6143065159184056</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No_Diploma_Pct</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.07166770475194298</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.07166770475194298</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,7 +1013,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3894135897442059</v>
+        <v>0.388669569617728</v>
       </c>
     </row>
     <row r="3">
@@ -935,7 +1026,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2281990658988461</v>
+        <v>0.2293747282980975</v>
       </c>
     </row>
     <row r="4">
@@ -948,7 +1039,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1602178027070498</v>
+        <v>0.155316374103922</v>
       </c>
     </row>
     <row r="5">
@@ -961,7 +1052,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09366662470638787</v>
+        <v>0.09053435737264807</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +1065,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0403950501766198</v>
+        <v>0.03588963830155308</v>
       </c>
     </row>
     <row r="7">
@@ -987,7 +1078,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02316921538315467</v>
+        <v>0.02252368618415291</v>
       </c>
     </row>
     <row r="8">
@@ -1000,7 +1091,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01885905450202271</v>
+        <v>0.01762227121437771</v>
       </c>
     </row>
     <row r="9">
@@ -1009,11 +1100,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>No_Diploma_Pct</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01180772737123504</v>
+        <v>0.01705184463301953</v>
       </c>
     </row>
     <row r="10">
@@ -1026,7 +1117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01177864178940644</v>
+        <v>0.01172194542024151</v>
       </c>
     </row>
     <row r="11">
@@ -1039,7 +1130,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01131077909198173</v>
+        <v>0.01119315151525525</v>
       </c>
     </row>
     <row r="12">
@@ -1052,7 +1143,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01118244862909001</v>
+        <v>0.01071810580835519</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No_Diploma_Pct</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.00938432753064929</v>
       </c>
     </row>
   </sheetData>
@@ -1091,10 +1195,10 @@
         <v>32.4</v>
       </c>
       <c r="B2" t="n">
-        <v>33.20544009895612</v>
+        <v>33.57316489426125</v>
       </c>
       <c r="C2" t="n">
-        <v>27.56100000000002</v>
+        <v>27.26050000000003</v>
       </c>
     </row>
     <row r="3">
@@ -1102,10 +1206,10 @@
         <v>17.6</v>
       </c>
       <c r="B3" t="n">
-        <v>17.07455640986205</v>
+        <v>16.97176569174942</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66700000000001</v>
+        <v>17.42900000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1113,10 +1217,10 @@
         <v>22.3</v>
       </c>
       <c r="B4" t="n">
-        <v>22.4530713991409</v>
+        <v>23.64622040919593</v>
       </c>
       <c r="C4" t="n">
-        <v>22.13250000000002</v>
+        <v>22.12700000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1124,10 +1228,10 @@
         <v>14.7</v>
       </c>
       <c r="B5" t="n">
-        <v>14.89983906991029</v>
+        <v>14.72916476034045</v>
       </c>
       <c r="C5" t="n">
-        <v>15.8785</v>
+        <v>15.78400000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1135,10 +1239,10 @@
         <v>34.7</v>
       </c>
       <c r="B6" t="n">
-        <v>30.75347695678834</v>
+        <v>32.69154872531953</v>
       </c>
       <c r="C6" t="n">
-        <v>27.93650000000003</v>
+        <v>27.42900000000003</v>
       </c>
     </row>
     <row r="7">
@@ -1146,10 +1250,10 @@
         <v>14.5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.02810278737209</v>
+        <v>14.56332376073581</v>
       </c>
       <c r="C7" t="n">
-        <v>17.639</v>
+        <v>17.743</v>
       </c>
     </row>
     <row r="8">
@@ -1157,10 +1261,10 @@
         <v>27.9</v>
       </c>
       <c r="B8" t="n">
-        <v>29.20235567928056</v>
+        <v>29.62821700382936</v>
       </c>
       <c r="C8" t="n">
-        <v>25.55949999999999</v>
+        <v>25.33549999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1168,10 +1272,10 @@
         <v>7.3</v>
       </c>
       <c r="B9" t="n">
-        <v>8.448603934836205</v>
+        <v>7.771128652725361</v>
       </c>
       <c r="C9" t="n">
-        <v>7.734000000000014</v>
+        <v>7.622000000000009</v>
       </c>
     </row>
     <row r="10">
@@ -1179,10 +1283,10 @@
         <v>10.2</v>
       </c>
       <c r="B10" t="n">
-        <v>13.93498258704197</v>
+        <v>12.10885777944365</v>
       </c>
       <c r="C10" t="n">
-        <v>11.51449999999999</v>
+        <v>11.45499999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1190,10 +1294,10 @@
         <v>30.5</v>
       </c>
       <c r="B11" t="n">
-        <v>32.02554713506264</v>
+        <v>34.97405971484054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.73499999999998</v>
+        <v>28.90899999999997</v>
       </c>
     </row>
     <row r="12">
@@ -1201,10 +1305,10 @@
         <v>11.6</v>
       </c>
       <c r="B12" t="n">
-        <v>9.605907446578499</v>
+        <v>8.78841985261894</v>
       </c>
       <c r="C12" t="n">
-        <v>12.695</v>
+        <v>12.493</v>
       </c>
     </row>
     <row r="13">
@@ -1212,10 +1316,10 @@
         <v>15.7</v>
       </c>
       <c r="B13" t="n">
-        <v>18.25603318043347</v>
+        <v>18.25791562167411</v>
       </c>
       <c r="C13" t="n">
-        <v>16.9165</v>
+        <v>17.0115</v>
       </c>
     </row>
     <row r="14">
@@ -1223,10 +1327,10 @@
         <v>23.5</v>
       </c>
       <c r="B14" t="n">
-        <v>24.33886621785751</v>
+        <v>25.26846182707266</v>
       </c>
       <c r="C14" t="n">
-        <v>22.57500000000002</v>
+        <v>22.1325</v>
       </c>
     </row>
     <row r="15">
@@ -1234,10 +1338,10 @@
         <v>20.8</v>
       </c>
       <c r="B15" t="n">
-        <v>20.02215004075246</v>
+        <v>20.49022294241108</v>
       </c>
       <c r="C15" t="n">
-        <v>17.89950000000002</v>
+        <v>17.883</v>
       </c>
     </row>
     <row r="16">
@@ -1245,10 +1349,10 @@
         <v>27.2</v>
       </c>
       <c r="B16" t="n">
-        <v>25.1481864012151</v>
+        <v>26.42832263955822</v>
       </c>
       <c r="C16" t="n">
-        <v>23.51500000000002</v>
+        <v>22.90350000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1256,10 +1360,10 @@
         <v>23.8</v>
       </c>
       <c r="B17" t="n">
-        <v>25.09132573532041</v>
+        <v>25.12449329774137</v>
       </c>
       <c r="C17" t="n">
-        <v>23.22200000000001</v>
+        <v>23.09200000000002</v>
       </c>
     </row>
     <row r="18">
@@ -1267,10 +1371,10 @@
         <v>23.4</v>
       </c>
       <c r="B18" t="n">
-        <v>22.77683718055563</v>
+        <v>22.39493605447059</v>
       </c>
       <c r="C18" t="n">
-        <v>22.199</v>
+        <v>21.99600000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1278,10 +1382,10 @@
         <v>13.4</v>
       </c>
       <c r="B19" t="n">
-        <v>12.35482612238885</v>
+        <v>11.43766296524007</v>
       </c>
       <c r="C19" t="n">
-        <v>15.42349999999997</v>
+        <v>15.54399999999998</v>
       </c>
     </row>
     <row r="20">
@@ -1289,10 +1393,10 @@
         <v>20.4</v>
       </c>
       <c r="B20" t="n">
-        <v>16.69485300647943</v>
+        <v>15.8969277614746</v>
       </c>
       <c r="C20" t="n">
-        <v>21.09900000000001</v>
+        <v>21.11100000000002</v>
       </c>
     </row>
     <row r="21">
@@ -1300,10 +1404,10 @@
         <v>18.7</v>
       </c>
       <c r="B21" t="n">
-        <v>14.7568939001441</v>
+        <v>14.81105890469367</v>
       </c>
       <c r="C21" t="n">
-        <v>16.33199999999999</v>
+        <v>16.17899999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1311,10 +1415,10 @@
         <v>10.5</v>
       </c>
       <c r="B22" t="n">
-        <v>12.4818565745114</v>
+        <v>12.08754958950548</v>
       </c>
       <c r="C22" t="n">
-        <v>13.43749999999999</v>
+        <v>13.3075</v>
       </c>
     </row>
     <row r="23">
@@ -1322,10 +1426,10 @@
         <v>45.5</v>
       </c>
       <c r="B23" t="n">
-        <v>37.47196941958128</v>
+        <v>37.78084354008886</v>
       </c>
       <c r="C23" t="n">
-        <v>34.20300000000001</v>
+        <v>33.466</v>
       </c>
     </row>
     <row r="24">
@@ -1333,10 +1437,10 @@
         <v>18.3</v>
       </c>
       <c r="B24" t="n">
-        <v>18.60753011671749</v>
+        <v>17.48773971777336</v>
       </c>
       <c r="C24" t="n">
-        <v>21.41600000000001</v>
+        <v>21.72250000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1344,10 +1448,10 @@
         <v>13.7</v>
       </c>
       <c r="B25" t="n">
-        <v>17.12959045334351</v>
+        <v>16.64619108681403</v>
       </c>
       <c r="C25" t="n">
-        <v>17.93450000000001</v>
+        <v>17.95800000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1355,10 +1459,10 @@
         <v>15</v>
       </c>
       <c r="B26" t="n">
-        <v>18.67979232386898</v>
+        <v>17.79278020554819</v>
       </c>
       <c r="C26" t="n">
-        <v>20.89700000000002</v>
+        <v>21.00150000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1366,10 +1470,10 @@
         <v>17.9</v>
       </c>
       <c r="B27" t="n">
-        <v>17.19495922323944</v>
+        <v>17.31309675995106</v>
       </c>
       <c r="C27" t="n">
-        <v>16.841</v>
+        <v>17.03449999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1377,10 +1481,10 @@
         <v>24.4</v>
       </c>
       <c r="B28" t="n">
-        <v>26.81283895898568</v>
+        <v>27.41702154023227</v>
       </c>
       <c r="C28" t="n">
-        <v>24.99500000000003</v>
+        <v>24.46050000000002</v>
       </c>
     </row>
     <row r="29">
@@ -1388,10 +1492,10 @@
         <v>11.4</v>
       </c>
       <c r="B29" t="n">
-        <v>11.33795672901558</v>
+        <v>11.85827945133852</v>
       </c>
       <c r="C29" t="n">
-        <v>14.03199999999999</v>
+        <v>14.11549999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1399,10 +1503,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="B30" t="n">
-        <v>8.587869084923522</v>
+        <v>9.074338843505418</v>
       </c>
       <c r="C30" t="n">
-        <v>7.089500000000012</v>
+        <v>7.286000000000012</v>
       </c>
     </row>
     <row r="31">
@@ -1410,10 +1514,10 @@
         <v>24.7</v>
       </c>
       <c r="B31" t="n">
-        <v>28.23421303002347</v>
+        <v>28.46417657419399</v>
       </c>
       <c r="C31" t="n">
-        <v>25.10400000000003</v>
+        <v>25.10800000000005</v>
       </c>
     </row>
     <row r="32">
@@ -1421,10 +1525,10 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>31.36490924330664</v>
+        <v>29.0131997710639</v>
       </c>
       <c r="C32" t="n">
-        <v>30.61449999999999</v>
+        <v>30.901</v>
       </c>
     </row>
     <row r="33">
@@ -1432,10 +1536,10 @@
         <v>15.9</v>
       </c>
       <c r="B33" t="n">
-        <v>16.87597961639037</v>
+        <v>15.88367576115932</v>
       </c>
       <c r="C33" t="n">
-        <v>18.63250000000001</v>
+        <v>18.76500000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1443,10 +1547,10 @@
         <v>18.6</v>
       </c>
       <c r="B34" t="n">
-        <v>20.89458459518977</v>
+        <v>20.40947767848076</v>
       </c>
       <c r="C34" t="n">
-        <v>22.21850000000001</v>
+        <v>22.16750000000002</v>
       </c>
     </row>
     <row r="35">
@@ -1454,10 +1558,10 @@
         <v>13.8</v>
       </c>
       <c r="B35" t="n">
-        <v>16.39756108377943</v>
+        <v>16.34762228313091</v>
       </c>
       <c r="C35" t="n">
-        <v>15.8015</v>
+        <v>15.9465</v>
       </c>
     </row>
     <row r="36">
@@ -1465,10 +1569,10 @@
         <v>10.5</v>
       </c>
       <c r="B36" t="n">
-        <v>12.07847569954093</v>
+        <v>13.00270717513294</v>
       </c>
       <c r="C36" t="n">
-        <v>14.8585</v>
+        <v>15.5765</v>
       </c>
     </row>
     <row r="37">
@@ -1476,10 +1580,10 @@
         <v>25.7</v>
       </c>
       <c r="B37" t="n">
-        <v>29.83924759353319</v>
+        <v>29.56223704127354</v>
       </c>
       <c r="C37" t="n">
-        <v>27.62899999999997</v>
+        <v>27.47249999999996</v>
       </c>
     </row>
     <row r="38">
@@ -1487,10 +1591,10 @@
         <v>10.3</v>
       </c>
       <c r="B38" t="n">
-        <v>12.8167163993421</v>
+        <v>12.7331846500011</v>
       </c>
       <c r="C38" t="n">
-        <v>13.765</v>
+        <v>13.9815</v>
       </c>
     </row>
     <row r="39">
@@ -1498,10 +1602,10 @@
         <v>12</v>
       </c>
       <c r="B39" t="n">
-        <v>18.00906156187074</v>
+        <v>17.61311996986961</v>
       </c>
       <c r="C39" t="n">
-        <v>15.42700000000001</v>
+        <v>15.5425</v>
       </c>
     </row>
     <row r="40">
@@ -1509,10 +1613,10 @@
         <v>18.5</v>
       </c>
       <c r="B40" t="n">
-        <v>12.97696810336186</v>
+        <v>12.98115743259426</v>
       </c>
       <c r="C40" t="n">
-        <v>11.18450000000001</v>
+        <v>10.68000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1520,10 +1624,10 @@
         <v>21.3</v>
       </c>
       <c r="B41" t="n">
-        <v>21.55103835930187</v>
+        <v>22.04044690980034</v>
       </c>
       <c r="C41" t="n">
-        <v>20.47099999999999</v>
+        <v>20.48899999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1531,10 +1635,10 @@
         <v>22.7</v>
       </c>
       <c r="B42" t="n">
-        <v>26.38049408769287</v>
+        <v>25.96954208280607</v>
       </c>
       <c r="C42" t="n">
-        <v>24.08850000000002</v>
+        <v>24.15450000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1542,10 +1646,10 @@
         <v>14.2</v>
       </c>
       <c r="B43" t="n">
-        <v>11.9282782574212</v>
+        <v>12.75558948637641</v>
       </c>
       <c r="C43" t="n">
-        <v>13.5775</v>
+        <v>13.7055</v>
       </c>
     </row>
   </sheetData>
